--- a/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten</t>
+          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 7,24</t>
+          <t>5,92; 7,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,22</t>
+          <t>6,49; 9,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 8,16</t>
+          <t>5,82; 8,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 6,71</t>
+          <t>5,6; 6,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,04</t>
+          <t>7,43; 9,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,42</t>
+          <t>6,43; 8,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,97; 6,75</t>
+          <t>5,93; 6,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 8,84</t>
+          <t>7,27; 8,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 8,01</t>
+          <t>6,5; 8,06</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,35</t>
+          <t>6,19; 7,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,29</t>
+          <t>7,59; 9,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 9,03</t>
+          <t>6,68; 8,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,05</t>
+          <t>5,75; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 9,21</t>
+          <t>7,61; 9,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,23; 7,61</t>
+          <t>6,24; 7,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 7,0</t>
+          <t>6,12; 7,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 8,92</t>
+          <t>7,78; 8,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 7,91</t>
+          <t>6,71; 8,06</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,29</t>
+          <t>5,69; 7,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,25</t>
+          <t>7,4; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,27</t>
+          <t>5,41; 8,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,09</t>
+          <t>5,65; 7,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,19</t>
+          <t>6,54; 8,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 8,58</t>
+          <t>6,4; 8,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,94; 6,96</t>
+          <t>5,88; 7,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 9,01</t>
+          <t>7,29; 9,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,08</t>
+          <t>6,27; 7,96</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 9,11</t>
+          <t>6,75; 9,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 8,49</t>
+          <t>6,73; 8,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,19</t>
+          <t>6,26; 8,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,65</t>
+          <t>6,94; 8,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,4</t>
+          <t>6,17; 8,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,55</t>
+          <t>5,59; 7,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,5</t>
+          <t>7,07; 8,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 8,11</t>
+          <t>6,66; 8,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 7,55</t>
+          <t>6,18; 7,62</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 7,71</t>
+          <t>6,57; 7,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,6</t>
+          <t>7,56; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,65; 7,84</t>
+          <t>6,62; 7,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,21</t>
+          <t>6,46; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 8,25</t>
+          <t>7,32; 8,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,4</t>
+          <t>6,5; 7,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,3</t>
+          <t>6,63; 7,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,27</t>
+          <t>7,54; 8,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 7,44</t>
+          <t>6,7; 7,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 7,17</t>
+          <t>5,85; 7,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,27</t>
+          <t>6,62; 9,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 8,11</t>
+          <t>6,02; 8,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 6,67</t>
+          <t>5,63; 6,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,15</t>
+          <t>7,38; 9,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 8,51</t>
+          <t>6,38; 8,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,93; 6,71</t>
+          <t>5,94; 6,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 8,8</t>
+          <t>7,33; 8,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,06</t>
+          <t>6,47; 7,97</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,38</t>
+          <t>6,19; 7,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 9,29</t>
+          <t>7,64; 9,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 8,88</t>
+          <t>6,67; 8,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,05</t>
+          <t>5,81; 7,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,61; 9,16</t>
+          <t>7,58; 9,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 7,62</t>
+          <t>6,22; 7,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,04</t>
+          <t>6,15; 7,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 8,91</t>
+          <t>7,74; 8,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,06</t>
+          <t>6,63; 7,99</t>
         </is>
       </c>
     </row>
@@ -897,42 +897,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 7,26</t>
+          <t>5,65; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 10,29</t>
+          <t>7,45; 10,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 8,23</t>
+          <t>5,37; 8,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,12</t>
+          <t>5,53; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 8,21</t>
+          <t>6,5; 8,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,49</t>
+          <t>6,44; 8,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,03</t>
+          <t>5,89; 6,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,05</t>
+          <t>7,22; 9,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,75; 9,21</t>
+          <t>6,78; 9,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,54</t>
+          <t>6,73; 8,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,29</t>
+          <t>6,26; 8,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,71</t>
+          <t>6,91; 8,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,17; 8,52</t>
+          <t>6,12; 8,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 7,71</t>
+          <t>5,5; 7,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 8,48</t>
+          <t>7,11; 8,53</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,12</t>
+          <t>6,66; 8,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,62</t>
+          <t>6,12; 7,59</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,65</t>
+          <t>6,62; 7,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 8,66</t>
+          <t>7,53; 8,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,82</t>
+          <t>6,62; 7,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,23</t>
+          <t>6,46; 7,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 8,25</t>
+          <t>7,29; 8,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 7,42</t>
+          <t>6,53; 7,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,25</t>
+          <t>6,62; 7,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,25</t>
+          <t>7,53; 8,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,44</t>
+          <t>6,7; 7,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,17</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,86</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,96</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 7,15</t>
+          <t>5,68; 6,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 9,26</t>
+          <t>7,4; 9,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,21</t>
+          <t>6,47; 8,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,68</t>
+          <t>5,96; 7,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 9,09</t>
+          <t>6,59; 9,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,38; 8,43</t>
+          <t>6,03; 8,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 6,71</t>
+          <t>5,97; 6,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 8,81</t>
+          <t>7,3; 8,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,97</t>
+          <t>6,46; 8,01</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,52</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,29</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,87</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>6,76</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>8,3</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,59</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,29</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,87</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,34</t>
+          <t>5,74; 7,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 9,44</t>
+          <t>7,56; 9,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,9</t>
+          <t>6,23; 7,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 7,05</t>
+          <t>6,21; 7,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,58; 9,23</t>
+          <t>7,53; 9,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,67</t>
+          <t>6,72; 9,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,04</t>
+          <t>6,09; 7,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 8,96</t>
+          <t>7,78; 8,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,99</t>
+          <t>6,67; 7,91</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,42</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,67</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,65</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,24</t>
+          <t>5,57; 7,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 10,41</t>
+          <t>6,5; 8,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,5</t>
+          <t>6,52; 8,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,14</t>
+          <t>5,77; 7,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 8,16</t>
+          <t>7,39; 10,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,46</t>
+          <t>5,29; 8,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 6,99</t>
+          <t>5,94; 6,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,06</t>
+          <t>7,18; 9,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 7,96</t>
+          <t>6,22; 8,08</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7,77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,48</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>7,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 9,35</t>
+          <t>6,94; 8,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 8,61</t>
+          <t>6,16; 8,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,26; 8,22</t>
+          <t>5,55; 7,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 8,78</t>
+          <t>6,68; 9,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,27</t>
+          <t>6,81; 8,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,44</t>
+          <t>6,31; 8,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,11; 8,53</t>
+          <t>7,1; 8,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 8,08</t>
+          <t>6,7; 8,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 7,59</t>
+          <t>6,16; 7,55</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,82</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,75</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,05</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>8,03</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,18</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,62</t>
+          <t>6,45; 7,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,6</t>
+          <t>7,24; 8,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,78</t>
+          <t>6,5; 7,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 7,3</t>
+          <t>6,6; 7,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 8,23</t>
+          <t>7,54; 8,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 7,45</t>
+          <t>6,65; 7,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,23</t>
+          <t>6,63; 7,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,53; 8,25</t>
+          <t>7,54; 8,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,46</t>
+          <t>6,71; 7,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3002_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Meses en la que empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer cereales con gluten (tasa de respuesta: 55,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,17</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,86</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.213635546949005</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.168644113015937</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>7.250080531539372</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.530402437048115</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>7.859068564649735</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.964623257929083</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>6.346214629537211</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>8.031069781129931</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.152614230883744</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>5,68; 6,71</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,4; 9,04</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6,47; 8,42</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 7,24</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,59; 9,22</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,03; 8,16</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>5,97; 6,75</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,3; 8,84</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6,46; 8,01</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>5.680152080432149</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7.402495656159248</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6.470593352323045</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>5.955247920401426</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>6.592356518464323</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>6.027339681748498</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>5.966224397920653</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.30050119328367</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>6.455417421104499</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.712825115347651</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>9.040226786677966</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.42480310604514</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.237101753858907</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>9.219693187861509</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.158709591426552</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>6.748020738286812</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>8.842487803526852</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>8.005640895503042</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,52</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,29</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,87</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,76</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,59</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,61</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>7,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,74; 7,05</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7,56; 9,21</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,23; 7,61</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6,21; 7,35</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,53; 9,29</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,72; 9,03</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,09; 7,0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,78; 8,92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6,67; 7,91</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.517122485892011</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8.290483031625843</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.867286666060399</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.756123722814791</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>8.304649811967572</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>7.587400813460853</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>6.610493291379286</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>8.297179771216207</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7.222302311275898</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,21</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8,67</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,65</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,46</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8,02</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7,08</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>5.739700878277309</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7.561529165910984</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>6.232672035743052</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>6.209903481613601</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>7.527988006035446</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>6.715271050183991</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.094478135635751</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.776999256347329</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6.671395100888679</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>5,57; 7,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 8,19</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>6,52; 8,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>5,77; 7,29</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>7,39; 10,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,29; 8,27</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>5,94; 6,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>7,18; 9,01</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>6,22; 8,08</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.045795114088918</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>9.210145929036567</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.608413984520441</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.350374546738564</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>9.293912469138432</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>9.028350589964097</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>7.001124710493964</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>8.924268031845424</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>7.911681183689139</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7,77</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,48</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,15</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,74</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,33</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.410797283462185</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.207884315554808</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.416156366665793</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.504902229447873</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>8.668986638797554</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.652297805018175</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>6.457608922615953</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>8.02020484747673</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>7.076956587630945</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>6,94; 8,65</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 8,4</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,55; 7,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6,68; 9,11</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 8,49</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,31; 8,19</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,1; 8,5</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6,7; 8,11</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 7,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>5.573157974244494</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>6.499801540516941</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.522150120302785</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>5.768720465738964</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>7.388192068296195</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.290169885638589</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>5.9413061598802</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>7.176499206794645</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>6.222803064534692</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.086490697335285</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>8.189997477768733</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.584834044388032</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.29163403550261</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10.24933904902471</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>8.272963839252689</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>6.962086244016581</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>9.013547483961791</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8.07736321852469</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>7.702656940442093</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.169736940869694</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.351365310161629</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7.773755180986173</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>7.47774691505691</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>7.148765972855528</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>7.7375107304809</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>7.333099093609061</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6.822939890016661</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6.940785997845952</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>6.155819720262887</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.548643283238565</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>6.682318703478043</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>6.810883271700195</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>6.308734944301733</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>7.09518729326495</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>6.704653331487625</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>6.156460196499493</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.645356141168488</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.403698472727912</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.553916373551153</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>9.114907361245587</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.488160958693943</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>8.185571036128071</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>8.499308718898121</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>8.113098743821729</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7.55416960934796</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6,82</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,96</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,03</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,18</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>6,93</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>7,89</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>6,45; 7,21</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,24; 8,25</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6,5; 7,4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6,6; 7,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 8,6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,65; 7,84</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,63; 7,3</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7,54; 8,27</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>6,71; 7,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>6.822719847473246</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7.75216690274168</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>6.959649362999465</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>7.053143212888728</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>8.027161076087387</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>7.181663256953189</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>6.926457027895867</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>7.889823322883939</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>7.066219650662475</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.452181120082636</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>7.242190413764787</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>6.495554457079209</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>6.595158176679551</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>7.535800690806722</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>6.649275634563104</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>6.631434753358413</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>7.535169563389721</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>6.710514255879593</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>7.212129497273281</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.247859579546075</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>7.396067577476522</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.711707834475336</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>8.598412508445227</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>7.842842043538039</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>7.301253312633758</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>8.265786637781819</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>7.442897687289489</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
